--- a/UI Logic .xlsx
+++ b/UI Logic .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/33704628a463f243/Desktop/Expense App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{D4221022-72CB-4F5E-8871-BC4DD7AE4894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20504D76-B603-4D3A-86C6-01F4158E71F8}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{D4221022-72CB-4F5E-8871-BC4DD7AE4894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CB2174F-D9A1-4680-BEAE-A425A2BB2FD3}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{0642423C-53F6-4199-84B2-084609B3FFE0}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0642423C-53F6-4199-84B2-084609B3FFE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">Logic </t>
   </si>
@@ -68,6 +68,33 @@
   </si>
   <si>
     <t>logic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column logic </t>
+  </si>
+  <si>
+    <t>run loop on the base of current year for jan to dec in which we make div for each month on expnese data which will align with col .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For Acutal data we can add all amount in div </t>
+  </si>
+  <si>
+    <t>Total Logic for actual data</t>
+  </si>
+  <si>
+    <t>Total Logic for Paid data</t>
+  </si>
+  <si>
+    <t>Same logic but on the basis of month and time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if st date == current year and current month == st month and current year &lt; end date then data goes to month div </t>
+  </si>
+  <si>
+    <t>if enddate &gt;year? If strt &lt;year ? div :if strt=year div</t>
+  </si>
+  <si>
+    <t>expense logic</t>
   </si>
 </sst>
 </file>
@@ -91,7 +118,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -101,6 +128,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -117,12 +150,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E4D010-D660-451D-B878-06FE11C5FB4D}">
-  <dimension ref="F12:I14"/>
+  <dimension ref="F12:I40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="8" max="8" width="23.7890625" bestFit="1" customWidth="1"/>
@@ -543,6 +577,44 @@
         <v>4</v>
       </c>
     </row>
+    <row r="35" spans="8:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="H35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="8:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="H36" s="3"/>
+      <c r="I36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="8:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="H37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="8:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="H38" t="s">
+        <v>10</v>
+      </c>
+      <c r="I38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="8:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="H40" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
